--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,1563 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128897729</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79710</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>616410</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6974905</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128897737</v>
+      </c>
+      <c r="B4" t="n">
+        <v>81105</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>616395</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6974813</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128897741</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78786</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>616493</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6974604</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128897727</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79710</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>616458</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6974771</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128897730</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>616410</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6974905</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128897735</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>616383</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6974907</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128897742</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>616486</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6974602</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128897731</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78878</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>616410</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6974905</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128897738</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92989</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>616424</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6974717</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128897740</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>616474</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6974642</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128897736</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>616379</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6974866</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128897733</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>616443</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6974995</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128897734</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>616428</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6974988</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128897732</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78786</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>353</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>616410</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6974905</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128897739</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>616463</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6974669</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128897726</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tormyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>616471</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6974602</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>79710</v>
+        <v>81105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R3" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>81105</v>
+        <v>79710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R4" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B3" t="n">
-        <v>81105</v>
+        <v>79710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R3" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B4" t="n">
-        <v>79710</v>
+        <v>81105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R4" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897730</v>
+        <v>128897742</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616410</v>
+        <v>616486</v>
       </c>
       <c r="R7" t="n">
-        <v>6974905</v>
+        <v>6974602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897735</v>
+        <v>128897730</v>
       </c>
       <c r="B8" t="n">
         <v>79739</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616383</v>
+        <v>616410</v>
       </c>
       <c r="R8" t="n">
-        <v>6974907</v>
+        <v>6974905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897742</v>
+        <v>128897735</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616486</v>
+        <v>616383</v>
       </c>
       <c r="R9" t="n">
-        <v>6974602</v>
+        <v>6974907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>79710</v>
+        <v>81109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R3" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>81105</v>
+        <v>79714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R4" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128897741</v>
+        <v>128897727</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>79714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616493</v>
+        <v>616458</v>
       </c>
       <c r="R5" t="n">
-        <v>6974604</v>
+        <v>6974771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128897727</v>
+        <v>128897741</v>
       </c>
       <c r="B6" t="n">
-        <v>79710</v>
+        <v>78790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616458</v>
+        <v>616493</v>
       </c>
       <c r="R6" t="n">
-        <v>6974771</v>
+        <v>6974604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897742</v>
+        <v>128897730</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616486</v>
+        <v>616410</v>
       </c>
       <c r="R7" t="n">
-        <v>6974602</v>
+        <v>6974905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897730</v>
+        <v>128897735</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616410</v>
+        <v>616383</v>
       </c>
       <c r="R8" t="n">
-        <v>6974905</v>
+        <v>6974907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897735</v>
+        <v>128897742</v>
       </c>
       <c r="B9" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616383</v>
+        <v>616486</v>
       </c>
       <c r="R9" t="n">
-        <v>6974907</v>
+        <v>6974602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>128897731</v>
       </c>
       <c r="B10" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128897740</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128897733</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128897734</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128897732</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128897739</v>
       </c>
       <c r="B17" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>128897726</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897730</v>
+        <v>128897742</v>
       </c>
       <c r="B7" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616410</v>
+        <v>616486</v>
       </c>
       <c r="R7" t="n">
-        <v>6974905</v>
+        <v>6974602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897735</v>
+        <v>128897730</v>
       </c>
       <c r="B8" t="n">
         <v>79743</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616383</v>
+        <v>616410</v>
       </c>
       <c r="R8" t="n">
-        <v>6974907</v>
+        <v>6974905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897742</v>
+        <v>128897735</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616486</v>
+        <v>616383</v>
       </c>
       <c r="R9" t="n">
-        <v>6974602</v>
+        <v>6974907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897739</v>
+        <v>128897726</v>
       </c>
       <c r="B17" t="n">
-        <v>79743</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,34 +2169,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616463</v>
+        <v>616471</v>
       </c>
       <c r="R17" t="n">
-        <v>6974669</v>
+        <v>6974602</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897726</v>
+        <v>128897739</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79743</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,39 +2271,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616471</v>
+        <v>616463</v>
       </c>
       <c r="R18" t="n">
-        <v>6974602</v>
+        <v>6974669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>81109</v>
+        <v>81014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128897727</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128897741</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897742</v>
+        <v>128897730</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616486</v>
+        <v>616410</v>
       </c>
       <c r="R7" t="n">
-        <v>6974602</v>
+        <v>6974905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897730</v>
+        <v>128897735</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616410</v>
+        <v>616383</v>
       </c>
       <c r="R8" t="n">
-        <v>6974905</v>
+        <v>6974907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897735</v>
+        <v>128897742</v>
       </c>
       <c r="B9" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616383</v>
+        <v>616486</v>
       </c>
       <c r="R9" t="n">
-        <v>6974907</v>
+        <v>6974602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>128897731</v>
       </c>
       <c r="B10" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128897740</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128897733</v>
       </c>
       <c r="B14" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128897734</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128897732</v>
       </c>
       <c r="B16" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128897726</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>128897739</v>
       </c>
       <c r="B18" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>81019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R3" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>81019</v>
+        <v>79624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R4" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B3" t="n">
-        <v>81019</v>
+        <v>79624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R3" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>81019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R4" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128897729</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128897737</v>
       </c>
       <c r="B4" t="n">
-        <v>81019</v>
+        <v>81020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128897741</v>
       </c>
       <c r="B5" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128897727</v>
       </c>
       <c r="B6" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897730</v>
+        <v>128897742</v>
       </c>
       <c r="B7" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616410</v>
+        <v>616486</v>
       </c>
       <c r="R7" t="n">
-        <v>6974905</v>
+        <v>6974602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897735</v>
+        <v>128897730</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616383</v>
+        <v>616410</v>
       </c>
       <c r="R8" t="n">
-        <v>6974907</v>
+        <v>6974905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897742</v>
+        <v>128897735</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616486</v>
+        <v>616383</v>
       </c>
       <c r="R9" t="n">
-        <v>6974602</v>
+        <v>6974907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>128897731</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128897740</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128897733</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128897734</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128897732</v>
       </c>
       <c r="B16" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897726</v>
+        <v>128897739</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,39 +2169,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616471</v>
+        <v>616463</v>
       </c>
       <c r="R17" t="n">
-        <v>6974602</v>
+        <v>6974669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897739</v>
+        <v>128897726</v>
       </c>
       <c r="B18" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,34 +2266,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616463</v>
+        <v>616471</v>
       </c>
       <c r="R18" t="n">
-        <v>6974669</v>
+        <v>6974602</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>79625</v>
+        <v>81020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R3" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>81020</v>
+        <v>79625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R4" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897742</v>
+        <v>128897730</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616486</v>
+        <v>616410</v>
       </c>
       <c r="R7" t="n">
-        <v>6974602</v>
+        <v>6974905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897730</v>
+        <v>128897735</v>
       </c>
       <c r="B8" t="n">
         <v>79654</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616410</v>
+        <v>616383</v>
       </c>
       <c r="R8" t="n">
-        <v>6974905</v>
+        <v>6974907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897735</v>
+        <v>128897742</v>
       </c>
       <c r="B9" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616383</v>
+        <v>616486</v>
       </c>
       <c r="R9" t="n">
-        <v>6974907</v>
+        <v>6974602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897739</v>
+        <v>128897726</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,34 +2169,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616463</v>
+        <v>616471</v>
       </c>
       <c r="R17" t="n">
-        <v>6974669</v>
+        <v>6974602</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897726</v>
+        <v>128897739</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,39 +2271,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616471</v>
+        <v>616463</v>
       </c>
       <c r="R18" t="n">
-        <v>6974602</v>
+        <v>6974669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B3" t="n">
-        <v>81020</v>
+        <v>79625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R3" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B4" t="n">
-        <v>79625</v>
+        <v>81020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R4" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128897741</v>
+        <v>128897727</v>
       </c>
       <c r="B5" t="n">
-        <v>78701</v>
+        <v>79625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616493</v>
+        <v>616458</v>
       </c>
       <c r="R5" t="n">
-        <v>6974604</v>
+        <v>6974771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128897727</v>
+        <v>128897741</v>
       </c>
       <c r="B6" t="n">
-        <v>79625</v>
+        <v>78701</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616458</v>
+        <v>616493</v>
       </c>
       <c r="R6" t="n">
-        <v>6974771</v>
+        <v>6974604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897726</v>
+        <v>128897739</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,39 +2169,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616471</v>
+        <v>616463</v>
       </c>
       <c r="R17" t="n">
-        <v>6974602</v>
+        <v>6974669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897739</v>
+        <v>128897726</v>
       </c>
       <c r="B18" t="n">
-        <v>79654</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,34 +2266,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616463</v>
+        <v>616471</v>
       </c>
       <c r="R18" t="n">
-        <v>6974669</v>
+        <v>6974602</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897730</v>
+        <v>128897742</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616410</v>
+        <v>616486</v>
       </c>
       <c r="R7" t="n">
-        <v>6974905</v>
+        <v>6974602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897735</v>
+        <v>128897730</v>
       </c>
       <c r="B8" t="n">
         <v>79654</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616383</v>
+        <v>616410</v>
       </c>
       <c r="R8" t="n">
-        <v>6974907</v>
+        <v>6974905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897742</v>
+        <v>128897735</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616486</v>
+        <v>616383</v>
       </c>
       <c r="R9" t="n">
-        <v>6974602</v>
+        <v>6974907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>79625</v>
+        <v>81024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R3" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>81020</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R4" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128897727</v>
+        <v>128897741</v>
       </c>
       <c r="B5" t="n">
-        <v>79625</v>
+        <v>78705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616458</v>
+        <v>616493</v>
       </c>
       <c r="R5" t="n">
-        <v>6974771</v>
+        <v>6974604</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128897741</v>
+        <v>128897727</v>
       </c>
       <c r="B6" t="n">
-        <v>78701</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616493</v>
+        <v>616458</v>
       </c>
       <c r="R6" t="n">
-        <v>6974604</v>
+        <v>6974771</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897742</v>
+        <v>128897730</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616486</v>
+        <v>616410</v>
       </c>
       <c r="R7" t="n">
-        <v>6974602</v>
+        <v>6974905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897730</v>
+        <v>128897735</v>
       </c>
       <c r="B8" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616410</v>
+        <v>616383</v>
       </c>
       <c r="R8" t="n">
-        <v>6974905</v>
+        <v>6974907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897735</v>
+        <v>128897742</v>
       </c>
       <c r="B9" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616383</v>
+        <v>616486</v>
       </c>
       <c r="R9" t="n">
-        <v>6974907</v>
+        <v>6974602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>128897731</v>
       </c>
       <c r="B10" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128897740</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128897733</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128897734</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128897732</v>
       </c>
       <c r="B16" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897739</v>
+        <v>128897726</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,34 +2169,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616463</v>
+        <v>616471</v>
       </c>
       <c r="R17" t="n">
-        <v>6974669</v>
+        <v>6974602</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897726</v>
+        <v>128897739</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,39 +2271,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616471</v>
+        <v>616463</v>
       </c>
       <c r="R18" t="n">
-        <v>6974602</v>
+        <v>6974669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897726</v>
+        <v>128897739</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>79658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,39 +2169,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616471</v>
+        <v>616463</v>
       </c>
       <c r="R17" t="n">
-        <v>6974602</v>
+        <v>6974669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897739</v>
+        <v>128897726</v>
       </c>
       <c r="B18" t="n">
-        <v>79658</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,34 +2266,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616463</v>
+        <v>616471</v>
       </c>
       <c r="R18" t="n">
-        <v>6974669</v>
+        <v>6974602</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>81024</v>
+        <v>81026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128897741</v>
       </c>
       <c r="B5" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128897727</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128897730</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128897735</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128897742</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128897731</v>
       </c>
       <c r="B10" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128897740</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128897733</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128897734</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128897732</v>
       </c>
       <c r="B16" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128897739</v>
       </c>
       <c r="B17" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>128897726</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B3" t="n">
-        <v>81026</v>
+        <v>79631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R3" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B4" t="n">
-        <v>79631</v>
+        <v>81026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R4" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128897729</v>
+        <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>79631</v>
+        <v>81026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616410</v>
+        <v>616395</v>
       </c>
       <c r="R3" t="n">
-        <v>6974905</v>
+        <v>6974813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128897737</v>
+        <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>81026</v>
+        <v>79631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616395</v>
+        <v>616410</v>
       </c>
       <c r="R4" t="n">
-        <v>6974813</v>
+        <v>6974905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>81026</v>
+        <v>81028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128897741</v>
+        <v>128897727</v>
       </c>
       <c r="B5" t="n">
-        <v>78707</v>
+        <v>79633</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616493</v>
+        <v>616458</v>
       </c>
       <c r="R5" t="n">
-        <v>6974604</v>
+        <v>6974771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128897727</v>
+        <v>128897741</v>
       </c>
       <c r="B6" t="n">
-        <v>79631</v>
+        <v>78709</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616458</v>
+        <v>616493</v>
       </c>
       <c r="R6" t="n">
-        <v>6974771</v>
+        <v>6974604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>128897730</v>
       </c>
       <c r="B7" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128897735</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128897742</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128897731</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128897740</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128897733</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128897734</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128897732</v>
       </c>
       <c r="B16" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128897739</v>
       </c>
       <c r="B17" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128897737</v>
       </c>
       <c r="B3" t="n">
-        <v>81028</v>
+        <v>81029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128897729</v>
       </c>
       <c r="B4" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128897727</v>
+        <v>128897741</v>
       </c>
       <c r="B5" t="n">
-        <v>79633</v>
+        <v>78710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616458</v>
+        <v>616493</v>
       </c>
       <c r="R5" t="n">
-        <v>6974771</v>
+        <v>6974604</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128897741</v>
+        <v>128897727</v>
       </c>
       <c r="B6" t="n">
-        <v>78709</v>
+        <v>79634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616493</v>
+        <v>616458</v>
       </c>
       <c r="R6" t="n">
-        <v>6974604</v>
+        <v>6974771</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128897730</v>
+        <v>128897742</v>
       </c>
       <c r="B7" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616410</v>
+        <v>616486</v>
       </c>
       <c r="R7" t="n">
-        <v>6974905</v>
+        <v>6974602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128897735</v>
+        <v>128897730</v>
       </c>
       <c r="B8" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616383</v>
+        <v>616410</v>
       </c>
       <c r="R8" t="n">
-        <v>6974907</v>
+        <v>6974905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128897742</v>
+        <v>128897735</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616486</v>
+        <v>616383</v>
       </c>
       <c r="R9" t="n">
-        <v>6974602</v>
+        <v>6974907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>128897731</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128897738</v>
       </c>
       <c r="B11" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128897740</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128897736</v>
       </c>
       <c r="B13" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128897733</v>
       </c>
       <c r="B14" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128897734</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128897732</v>
       </c>
       <c r="B16" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128897739</v>
       </c>
       <c r="B17" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 14582-2024 artfynd.xlsx
+++ b/artfynd/A 14582-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897732</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897741</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897724</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897737</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897736</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897738</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270031</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897734</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897740</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897742</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897730</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897733</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897735</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897739</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897726</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897731</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897727</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897729</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2528,8 +2623,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>